--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-06.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-06.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583981810515</v>
+        <v>5583988443608</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Edilson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michelle Silva Sousa</t>
+          <t>Edilson de Araujo Gomes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583987826990</v>
+        <v>5583994066976</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flaviano</t>
+          <t>Incomel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Flaviano Navarro</t>
+          <t>Incomel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583981331285</v>
+        <v>5581982200917</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Patricio Alexandre Jesus Pereira</t>
+          <t>Ana Carolina dos Santos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987814264</v>
+        <v>5583981810515</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daniiele</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Daniiele da Conceicao de Lima</t>
+          <t>Michelle Silva Sousa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583986677820</v>
+        <v>5583987826990</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Catia</t>
+          <t>Flaviano</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Catia Lourdes Silva de Souza</t>
+          <t>Flaviano Navarro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583993542493</v>
+        <v>5583981331285</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maria da Gloria Cartaxo Alves</t>
+          <t>Patricio Alexandre Jesus Pereira</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583986000023</v>
+        <v>5583987814264</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Daniiele</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clara Balbino</t>
+          <t>Daniiele da Conceicao de Lima</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5581988605912</v>
+        <v>5583986677820</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Catia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paulo Cesar Amorim</t>
+          <t>Catia Lourdes Silva de Souza</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987289208</v>
+        <v>5583993542493</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Valdeilzo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Valdeilzo Barbosa Figueiredo</t>
+          <t>Maria da Gloria Cartaxo Alves</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583996845032</v>
+        <v>5583986000023</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hevellyn</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hevellyn de Barros Brito</t>
+          <t>Clara Balbino</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583991277009</v>
+        <v>5581988605912</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manoel Patricio de Souza Neto</t>
+          <t>Paulo Cesar Amorim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583988771558</v>
+        <v>5583987289208</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adriano</t>
+          <t>Valdeilzo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adriano Adelino de Farias</t>
+          <t>Valdeilzo Barbosa Figueiredo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583993721478</v>
+        <v>5583996845032</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Francicleide</t>
+          <t>Hevellyn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Francicleide Dutra da Silva</t>
+          <t>Hevellyn de Barros Brito</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583986226309</v>
+        <v>5583991277009</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marinez</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marinez Gomes</t>
+          <t>Manoel Patricio de Souza Neto</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583996369046</v>
+        <v>5583988771558</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Helenisio</t>
+          <t>Adriano</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Helenisio Francisco dos Santos Junior</t>
+          <t>Adriano Adelino de Farias</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988816816</v>
+        <v>5583993721478</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Francicleide</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Farah Aparecida da Cunha</t>
+          <t>Francicleide Dutra da Silva</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583993434318</v>
+        <v>5583986226309</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Francinaldo</t>
+          <t>Marinez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Francinaldo Almeida Torres</t>
+          <t>Marinez Gomes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583993821006</v>
+        <v>5583996369046</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Helenisio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lucas Chateaubriant</t>
+          <t>Helenisio Francisco dos Santos Junior</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583987055064</v>
+        <v>5583988816816</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jose Aurelio Batista de Sousa</t>
+          <t>Farah Aparecida da Cunha</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583981116500</v>
+        <v>5583993434318</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Joallysson</t>
+          <t>Francinaldo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Joallysson Robson Santos da Silva</t>
+          <t>Francinaldo Almeida Torres</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583987096317</v>
+        <v>5583993821006</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jose Ivanildo Bandeira de França</t>
+          <t>Lucas Chateaubriant</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583981762509</v>
+        <v>5583987055064</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Isaac Galvao Barbosa</t>
+          <t>Jose Aurelio Batista de Sousa</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5511980196144</v>
+        <v>5583981116500</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Joallysson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edificio Moreira</t>
+          <t>Joallysson Robson Santos da Silva</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583998040918</v>
+        <v>5583987096317</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Construtora</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Construtora Colombo</t>
+          <t>Jose Ivanildo Bandeira de França</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583991049990</v>
+        <v>5583981762509</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fabio Santos da Hora</t>
+          <t>Isaac Galvao Barbosa</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583988930793</v>
+        <v>5511980196144</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva Ferreira</t>
+          <t>Edificio Moreira</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583994104514</v>
+        <v>5583998040918</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>Construtora</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Matheus Henrique Iwagoe Silva</t>
+          <t>Construtora Colombo</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583981183961</v>
+        <v>5583991049990</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Helania</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Helania Cristina de Oliveira Damascena</t>
+          <t>Fabio Santos da Hora</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583996362555</v>
+        <v>5583988930793</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vanessa Carla Souza Cabral</t>
+          <t>Ana Flavia Silva Ferreira</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583988963195</v>
+        <v>5583994104514</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alecsandro</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alecsandro Gomes da Silva</t>
+          <t>Matheus Henrique Iwagoe Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583985959588</v>
+        <v>5583981183961</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Valdete</t>
+          <t>Helania</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valdete Alves dos Santos</t>
+          <t>Helania Cristina de Oliveira Damascena</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583988885098</v>
+        <v>5583996362555</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monica Maria Gomes</t>
+          <t>Vanessa Carla Souza Cabral</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583993814002</v>
+        <v>5583988963195</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Alecsandro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Edson da Silva Pereira</t>
+          <t>Alecsandro Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583999392259</v>
+        <v>5583985959588</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Williane</t>
+          <t>Valdete</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Williane Kevelyn Silva do Nascimento</t>
+          <t>Valdete Alves dos Santos</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583981856147</v>
+        <v>5583988885098</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Simone Lima</t>
+          <t>Monica Maria Gomes</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583986724345</v>
+        <v>5583993814002</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blandina</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Blandina Teixeira de Lima</t>
+          <t>Edson da Silva Pereira</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583987491316</v>
+        <v>5583999392259</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nielly</t>
+          <t>Williane</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nielly Regina do Nascimento Barbosa</t>
+          <t>Williane Kevelyn Silva do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583981397533</v>
+        <v>5583981856147</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Maria de Lourdes Gomes Alves</t>
+          <t>Simone Lima</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583999757883</v>
+        <v>5583986724345</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Edilson</t>
+          <t>Blandina</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edilson Costa Dias</t>
+          <t>Blandina Teixeira de Lima</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5511994650480</v>
+        <v>5583987491316</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Weverky</t>
+          <t>Nielly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Weverky da Silva</t>
+          <t>Nielly Regina do Nascimento Barbosa</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583999653295</v>
+        <v>5583981397533</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cristiane Kelly F da Silva</t>
+          <t>Maria de Lourdes Gomes Alves</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583996920670</v>
+        <v>5583999757883</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Willianne</t>
+          <t>Edilson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Willianne Brasiliano de Lima</t>
+          <t>Edilson Costa Dias</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583981501727</v>
+        <v>5511994650480</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Edvaldir</t>
+          <t>Weverky</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edvaldir de Oliveira Tintino Junior</t>
+          <t>Weverky da Silva</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988141508</v>
+        <v>5583999653295</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jose da Silva Camilo</t>
+          <t>Cristiane Kelly F da Silva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583987791825</v>
+        <v>5583996920670</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Willianne</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vera Lucia Pinto</t>
+          <t>Willianne Brasiliano de Lima</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583986159171</v>
+        <v>5583981501727</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cosmo</t>
+          <t>Edvaldir</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cosmo da Silva Cordeiro</t>
+          <t>Edvaldir de Oliveira Tintino Junior</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583994169420</v>
+        <v>5583988141508</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Edvaldo</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Edvaldo Silva Alves</t>
+          <t>Jose da Silva Camilo</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583988266369</v>
+        <v>5583987791825</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Construtora</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Construtora Britales</t>
+          <t>Vera Lucia Pinto</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583987967522</v>
+        <v>5583986159171</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mikael</t>
+          <t>Cosmo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mikael Patrick Soares Souza e Silva</t>
+          <t>Cosmo da Silva Cordeiro</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583996612472</v>
+        <v>5583994169420</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Giancarlos</t>
+          <t>Edvaldo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Giancarlos Tavares de Moura</t>
+          <t>Edvaldo Silva Alves</t>
         </is>
       </c>
     </row>
